--- a/artfynd/A 28267-2026 artfynd.xlsx
+++ b/artfynd/A 28267-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588185</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588186</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588188</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588190</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588193</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397128</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588180</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588192</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397129</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588181</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1992,6 +2052,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588183</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397123</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2186,6 +2256,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397124</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2283,6 +2358,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397127</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2393,6 +2473,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588195</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2499,6 +2584,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397130</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2605,6 +2695,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129397131</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588179</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2823,6 +2923,11 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Karlstads Kommun - NVI Sörmon</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588194</t>
         </is>
       </c>
     </row>
@@ -2941,8 +3046,36 @@
           <t>Karlstads Kommun - NVI Sörmon</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121588196</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>